--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4768,8 +4768,8 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
@@ -6118,7 +6118,7 @@
         <v>4</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11743,8 +11743,8 @@
       <c r="P114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" s="9" t="n">
-        <v>1</v>
+      <c r="Q114" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18060,8 +18060,8 @@
       <c r="T179" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U179" s="9" t="n">
-        <v>0</v>
+      <c r="U179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V179" s="9" t="n">
         <v>0</v>
@@ -18498,7 +18498,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18960,7 +18960,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -19389,7 +19389,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 76 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 65 clubs short</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1573,8 +1573,8 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>3</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2167,8 +2167,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3331,8 +3331,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4883,8 +4883,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5245,7 +5245,7 @@
         <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6241,8 +6241,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7502,8 +7502,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14262,8 +14262,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P140" s="9" t="n">
-        <v>3</v>
+      <c r="P140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q140" s="10" t="n">
         <v>2</v>
@@ -14751,7 +14751,7 @@
         <v>0</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15941,8 +15941,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16135,8 +16135,8 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16214,8 +16214,8 @@
       <c r="S160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T160" s="9" t="n">
-        <v>0</v>
+      <c r="T160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U160" s="9" t="n">
         <v>0</v>
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R164" s="9" t="n">
         <v>0</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18075,8 +18075,8 @@
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="9" t="n">
-        <v>0</v>
+      <c r="Z179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA179" s="10" t="n">
         <v>1</v>
@@ -18300,7 +18300,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18333,7 +18333,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18399,7 +18399,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18498,7 +18498,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18531,7 +18531,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18597,7 +18597,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18696,7 +18696,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19158,7 +19158,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19290,7 +19290,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -19389,7 +19389,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 65 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 31 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA180"/>
+  <dimension ref="A1:AA181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -1003,8 +1003,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1676,8 +1676,8 @@
       <c r="W10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>0</v>
+      <c r="X10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>0</v>
@@ -2749,8 +2749,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4010,8 +4010,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4689,8 +4689,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5174,8 +5174,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5756,8 +5756,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6047,8 +6047,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -6223,11 +6223,11 @@
       <c r="S57" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="9" t="n">
-        <v>0</v>
+      <c r="T57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V57" s="9" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6338,8 +6338,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7017,8 +7017,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7230,11 +7230,11 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>5522829</v>
+        <v>28680688</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Entrepreneur Toastmasters Club</t>
+          <t>Entrepreneur Toastmasters 2</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7302,8 +7302,8 @@
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="10" t="n">
-        <v>4</v>
+      <c r="X68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -7327,15 +7327,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1249</v>
+        <v>5522829</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Life Enriching Toastmasters</t>
+          <t>Entrepreneur Toastmasters Club</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7349,17 +7349,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>0</v>
@@ -7385,22 +7385,22 @@
         <v>0</v>
       </c>
       <c r="S69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T69" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T69" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X69" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
@@ -7424,15 +7424,15 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>8020</v>
+        <v>1249</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Sustainably Speaking</t>
+          <t>Life Enriching Toastmasters</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7446,17 +7446,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L70" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7473,19 +7473,19 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7521,15 +7521,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>28677135</v>
+        <v>8020</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Toast to Water</t>
+          <t>Sustainably Speaking</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7543,17 +7543,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="9" t="n">
         <v>0</v>
@@ -7588,19 +7588,19 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -7618,15 +7618,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>28678724</v>
+        <v>28677135</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Urban League of Greater Southwestern Ohio Toastmasters</t>
+          <t>Toast to Water</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7640,17 +7640,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -7696,8 +7696,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -7711,19 +7711,19 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>28678579</v>
+        <v>28678724</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1% Better Together Toastmasters</t>
+          <t>Urban League of Greater Southwestern Ohio Toastmasters</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7782,19 +7782,19 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X73" s="9" t="n">
-        <v>0</v>
+      <c r="X73" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -7812,15 +7812,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>7083</v>
+        <v>28678579</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Cheers Toastmasters</t>
+          <t>1% Better Together Toastmasters</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7834,17 +7834,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -7879,19 +7879,19 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="10" t="n">
-        <v>1</v>
+      <c r="Z74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -7909,15 +7909,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3459</v>
+        <v>7083</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Great American Speakers Club</t>
+          <t>Cheers Toastmasters</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -7957,11 +7957,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P75" s="10" t="n">
-        <v>4</v>
+      <c r="P75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -7969,20 +7969,20 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="10" t="n">
-        <v>1</v>
+      <c r="T75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="10" t="n">
-        <v>5</v>
+      <c r="X75" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8006,15 +8006,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>9056</v>
+        <v>3459</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Speak With US</t>
+          <t>Great American Speakers Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8054,11 +8054,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P76" s="9" t="n">
-        <v>0</v>
+      <c r="P76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8066,14 +8066,14 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8103,15 +8103,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>9531</v>
+        <v>9056</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Toast Of Broadway Toastmasters Club</t>
+          <t>Speak With US</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,17 +8125,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8169,20 +8169,20 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="10" t="n">
-        <v>4</v>
+      <c r="V77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="10" t="n">
-        <v>1</v>
+      <c r="Z77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8200,15 +8200,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>742749</v>
+        <v>9531</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>TOASTMASTERS ON THE RHINE</t>
+          <t>Toast Of Broadway Toastmasters Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8266,14 +8266,14 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>2</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8293,15 +8293,15 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>922412</v>
+        <v>742749</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>American Modern Toastmasters</t>
+          <t>TOASTMASTERS ON THE RHINE</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8363,20 +8363,20 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="10" t="n">
-        <v>4</v>
+      <c r="V79" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8394,15 +8394,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>28677429</v>
+        <v>922412</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>CinToast 2.0</t>
+          <t>American Modern Toastmasters</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8416,17 +8416,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -8460,20 +8460,20 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>0</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X80" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8491,15 +8491,15 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>28679311</v>
+        <v>28677429</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>ICGC Speak &amp; Lead Club</t>
+          <t>CinToast 2.0</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,17 +8513,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -8564,13 +8564,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -8588,15 +8588,15 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>642205</v>
+        <v>28679311</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Mason Speech Weavers</t>
+          <t>ICGC Speak &amp; Lead Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -8637,16 +8637,16 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" s="9" t="n">
         <v>0</v>
@@ -8655,19 +8655,19 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X82" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="10" t="n">
-        <v>1</v>
+      <c r="Z82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>5008</v>
+        <v>642205</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Mason Town Criers Toastmasters Club</t>
+          <t>Mason Speech Weavers</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -8707,17 +8707,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -8734,16 +8734,16 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" s="9" t="n">
         <v>0</v>
@@ -8752,13 +8752,13 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X83" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -8782,15 +8782,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>2289</v>
+        <v>5008</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Milford T.A.L.K. Club</t>
+          <t>Mason Town Criers Toastmasters Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -8849,19 +8849,19 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -8875,15 +8875,15 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>3265258</v>
+        <v>2289</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>ADM City Center</t>
+          <t>Milford T.A.L.K. Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
         <v>0</v>
@@ -8915,11 +8915,11 @@
         </is>
       </c>
       <c r="M85" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O85" s="7" t="inlineStr">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -8951,8 +8951,8 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="9" t="n">
-        <v>0</v>
+      <c r="X85" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
@@ -8960,8 +8960,8 @@
       <c r="Z85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA85" s="9" t="n">
-        <v>0</v>
+      <c r="AA85" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -8976,15 +8976,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>8416</v>
+        <v>3265258</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Articulate Revenuers Toastmasters Club</t>
+          <t>ADM City Center</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9012,11 +9012,11 @@
         </is>
       </c>
       <c r="M86" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O86" s="7" t="inlineStr">
@@ -9043,22 +9043,22 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="10" t="n">
-        <v>5</v>
+      <c r="X86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA86" s="10" t="n">
-        <v>1</v>
+      <c r="Z86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -9073,15 +9073,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1223</v>
+        <v>8416</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Newport Toastmasters Club</t>
+          <t>Articulate Revenuers Toastmasters Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9098,10 +9098,10 @@
         <v>16</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
@@ -9133,20 +9133,20 @@
       <c r="S87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T87" s="10" t="n">
-        <v>1</v>
+      <c r="T87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>3</v>
+      <c r="X87" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9170,15 +9170,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>453</v>
+        <v>1223</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Pioneer Toastmasters Club</t>
+          <t>Newport Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9230,8 +9230,8 @@
       <c r="S88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="X88" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9267,11 +9267,11 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>1153372</v>
+        <v>453</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Voice of Independence</t>
+          <t>Pioneer Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9319,13 +9319,13 @@
         <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" s="10" t="n">
         <v>1</v>
@@ -9334,13 +9334,13 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9360,43 +9360,43 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>472</v>
+        <v>1153372</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Cincinnati Toastmasters</t>
+          <t>Voice of Independence</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K90" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F90" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K90" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>1</v>
@@ -9422,16 +9422,16 @@
         <v>0</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U90" s="9" t="n">
-        <v>0</v>
+      <c r="U90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9461,15 +9461,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>8634</v>
+        <v>472</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Ethicon Toastmasters Leaders In Speaking (TLS)</t>
+          <t>Cincinnati Toastmasters</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9483,17 +9483,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9521,20 +9521,20 @@
       <c r="S91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T91" s="9" t="n">
-        <v>0</v>
+      <c r="T91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="9" t="n">
-        <v>1</v>
+      <c r="X91" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -9558,15 +9558,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>907534</v>
+        <v>8634</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>FTMT on Campus</t>
+          <t>Ethicon Toastmasters Leaders In Speaking (TLS)</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,17 +9580,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -9606,17 +9606,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P92" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q92" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R92" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S92" s="10" t="n">
-        <v>2</v>
+      <c r="P92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -9631,13 +9631,13 @@
         <v>0</v>
       </c>
       <c r="X92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -9655,15 +9655,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>7335430</v>
+        <v>907534</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Givaudan Toastmasters</t>
+          <t>FTMT on Campus</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,17 +9677,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -9703,26 +9703,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+      <c r="P93" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q93" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R93" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S93" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -9733,8 +9733,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -9752,15 +9752,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>28679871</v>
+        <v>7335430</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>PECO Toastmasters Club</t>
+          <t>Givaudan Toastmasters</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,17 +9774,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -9849,15 +9849,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>7780</v>
+        <v>28679871</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Toast of the Town, Kenwood Toastmasters Club</t>
+          <t>PECO Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,17 +9871,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -9916,19 +9916,19 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X95" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="10" t="n">
-        <v>1</v>
+      <c r="Z95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -9942,43 +9942,43 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1160434</v>
+        <v>7780</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>BTC (Building Tomorrow's Communicators)</t>
+          <t>Toast of the Town, Kenwood Toastmasters Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K96" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10006,14 +10006,14 @@
       <c r="S96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T96" s="10" t="n">
-        <v>1</v>
+      <c r="T96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10043,15 +10043,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>4677366</v>
+        <v>1160434</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Competitive Speakers Cincinnati</t>
+          <t>BTC (Building Tomorrow's Communicators)</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10103,26 +10103,26 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="9" t="n">
-        <v>1</v>
+      <c r="X97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10140,15 +10140,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>1578</v>
+        <v>4677366</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Seven Hills of Cincinnati Toastmasters</t>
+          <t>Competitive Speakers Cincinnati</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10212,14 +10212,14 @@
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="10" t="n">
-        <v>5</v>
+      <c r="X98" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="10" t="n">
-        <v>1</v>
+      <c r="Z98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10237,11 +10237,11 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>3804</v>
+        <v>1578</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>The Kings Speech</t>
+          <t>Seven Hills of Cincinnati Toastmasters</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
         <v>0</v>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10334,11 +10334,11 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>9523</v>
+        <v>3804</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>TV Toastmasters Club</t>
+          <t>The Kings Speech</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10401,13 +10401,13 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="9" t="n">
-        <v>3</v>
+      <c r="X100" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -10422,20 +10422,20 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>3663553</v>
+        <v>9523</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Big Blue Toastmasters</t>
+          <t>TV Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10482,14 +10482,14 @@
       <c r="P101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" s="10" t="n">
-        <v>2</v>
+      <c r="Q101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" s="9" t="n">
         <v>0</v>
@@ -10498,19 +10498,19 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="10" t="n">
-        <v>4</v>
+      <c r="X101" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10528,11 +10528,11 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>7305</v>
+        <v>3663553</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Downtown Lunch Bunch Toastmasters Club</t>
+          <t>Big Blue Toastmasters</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10577,11 +10577,11 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
       </c>
@@ -10595,19 +10595,19 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="10" t="n">
-        <v>1</v>
+      <c r="Z102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>2391</v>
+        <v>7305</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Lexington Toastmasters Club</t>
+          <t>Downtown Lunch Bunch Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10674,11 +10674,11 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q103" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
       </c>
@@ -10691,11 +10691,11 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="10" t="n">
-        <v>4</v>
+      <c r="V103" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>6</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2949</v>
+        <v>2391</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Sunrise Toastmasters Club</t>
+          <t>Lexington Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -10773,29 +10773,29 @@
       <c r="P104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" s="9" t="n">
-        <v>0</v>
+      <c r="Q104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>1</v>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="X104" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -10819,15 +10819,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>5517</v>
+        <v>2949</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Xerox-Lexmark Lexington Toastmasters Club</t>
+          <t>Sunrise Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,17 +10841,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -10879,26 +10879,26 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="10" t="n">
-        <v>4</v>
+      <c r="X105" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -10912,19 +10912,19 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28680239</v>
+        <v>5517</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Coil Club</t>
+          <t>Xerox-Lexmark Lexington Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,17 +10938,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -10983,19 +10983,19 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>1</v>
+      <c r="X106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11013,15 +11013,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>2869</v>
+        <v>28680239</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Huntington Centennial Toastmasters Club</t>
+          <t>Coil Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,17 +11035,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11085,14 +11085,14 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="10" t="n">
-        <v>5</v>
+      <c r="X107" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="10" t="n">
-        <v>1</v>
+      <c r="Z107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>1990654</v>
+        <v>2869</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Midway Toastmasters</t>
+          <t>Huntington Centennial Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11159,31 +11159,31 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q108" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U108" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11207,15 +11207,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>6977905</v>
+        <v>1990654</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Mountain Movers</t>
+          <t>Midway Toastmasters</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,17 +11229,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11256,37 +11256,37 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11304,15 +11304,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28678791</v>
+        <v>6977905</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Vital Voices Toastmasters</t>
+          <t>Mountain Movers</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11355,8 +11355,8 @@
       <c r="P110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" s="10" t="n">
-        <v>2</v>
+      <c r="Q110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -11371,19 +11371,19 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="9" t="n">
-        <v>0</v>
+      <c r="X110" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -11397,19 +11397,19 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1129</v>
+        <v>28678791</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Communicators Club</t>
+          <t>Vital Voices Toastmasters</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11450,16 +11450,16 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S111" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="S111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T111" s="9" t="n">
         <v>0</v>
@@ -11468,13 +11468,13 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="10" t="n">
-        <v>5</v>
+      <c r="X111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11498,15 +11498,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>2410414</v>
+        <v>1129</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>GE Appliance Park Toastmasters</t>
+          <t>Communicators Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11547,16 +11547,16 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -11565,19 +11565,19 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="9" t="n">
-        <v>1</v>
+      <c r="X112" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11595,11 +11595,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1035</v>
+        <v>2410414</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Kentucky Farm Bureau Club</t>
+          <t>GE Appliance Park Toastmasters</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -11617,10 +11617,10 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K113" s="4" t="n">
         <v>0</v>
@@ -11667,8 +11667,8 @@
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="10" t="n">
-        <v>5</v>
+      <c r="X113" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>5035935</v>
+        <v>1035</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Lou City Toasters</t>
+          <t>Kentucky Farm Bureau Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,17 +11714,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -11743,14 +11743,14 @@
       <c r="P114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" s="10" t="n">
-        <v>2</v>
+      <c r="Q114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T114" s="9" t="n">
         <v>0</v>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -11770,8 +11770,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="10" t="n">
-        <v>1</v>
+      <c r="Z114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -11789,15 +11789,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>5104</v>
+        <v>5035935</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>St. Matthews/Lyndon Toastmasters Club</t>
+          <t>Lou City Toasters</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11838,31 +11838,31 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q115" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S115" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V115" s="10" t="n">
-        <v>4</v>
+      <c r="T115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -11882,19 +11882,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>8307</v>
+        <v>5104</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Gilded Tongues Club</t>
+          <t>St. Matthews/Lyndon Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,17 +11908,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -11935,37 +11935,37 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -11983,11 +11983,11 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>740597</v>
+        <v>8307</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Humana's Guiding Voices Club</t>
+          <t>Gilded Tongues Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -12005,10 +12005,10 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K117" s="4" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1990665</v>
+        <v>740597</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Legendary Communicators' Club</t>
+          <t>Humana's Guiding Voices Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,10 +12102,10 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>0</v>
@@ -12129,16 +12129,16 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12153,13 +12153,13 @@
         <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="10" t="n">
-        <v>1</v>
+      <c r="Z118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28677901</v>
+        <v>1990665</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Norton Brownsboro Toastmasters Club</t>
+          <t>Legendary Communicators' Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,25 +12199,25 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K119" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O119" s="7" t="inlineStr">
@@ -12226,16 +12226,16 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" s="9" t="n">
         <v>0</v>
@@ -12255,11 +12255,11 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA119" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>757850</v>
+        <v>28677901</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Peace Speakers Toastmasters Club</t>
+          <t>Norton Brownsboro Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,25 +12296,25 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O120" s="7" t="inlineStr">
@@ -12334,20 +12334,20 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="10" t="n">
-        <v>1</v>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -12355,8 +12355,8 @@
       <c r="Z120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA120" s="10" t="n">
-        <v>1</v>
+      <c r="AA120" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -12367,19 +12367,19 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>2832962</v>
+        <v>757850</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Best Side Toastmasters Club</t>
+          <t>Peace Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12431,26 +12431,26 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="9" t="n">
-        <v>0</v>
+      <c r="X121" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12468,15 +12468,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>3506</v>
+        <v>2832962</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Crescent City Toastmasters</t>
+          <t>Best Side Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12528,26 +12528,26 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="10" t="n">
-        <v>1</v>
+      <c r="T122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="10" t="n">
-        <v>5</v>
+      <c r="X122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="10" t="n">
-        <v>1</v>
+      <c r="Z122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>337</v>
+        <v>3506</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Evansville Number One Club</t>
+          <t>Crescent City Toastmasters</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12625,26 +12625,26 @@
       <c r="S123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>3</v>
+      <c r="X123" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28678031</v>
+        <v>337</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Gaseous Discussers</t>
+          <t>Evansville Number One Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,10 +12684,10 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>0</v>
@@ -12698,11 +12698,11 @@
         </is>
       </c>
       <c r="M124" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O124" s="7" t="inlineStr">
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -12734,8 +12734,8 @@
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="10" t="n">
-        <v>4</v>
+      <c r="X124" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12743,8 +12743,8 @@
       <c r="Z124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA124" s="9" t="n">
-        <v>0</v>
+      <c r="AA124" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>5045394</v>
+        <v>28678031</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Kentuckiana Women In Leadership</t>
+          <t>Gaseous Discussers</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,10 +12781,10 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K125" s="4" t="n">
         <v>0</v>
@@ -12795,11 +12795,11 @@
         </is>
       </c>
       <c r="M125" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O125" s="7" t="inlineStr">
@@ -12832,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12840,27 +12840,27 @@
       <c r="Z125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA125" s="10" t="n">
-        <v>1</v>
+      <c r="AA125" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>5581</v>
+        <v>5045394</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Club</t>
+          <t>Kentuckiana Women In Leadership</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>0</v>
@@ -12929,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -12953,11 +12953,11 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>8911</v>
+        <v>5581</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Golden Gavel Club</t>
+          <t>Dynamic Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -12975,17 +12975,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K127" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13026,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>6893</v>
+        <v>8911</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Indy Free Speakers Toastmasters Club</t>
+          <t>Golden Gavel Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13098,8 +13098,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P128" s="10" t="n">
-        <v>4</v>
+      <c r="P128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
@@ -13110,20 +13110,20 @@
       <c r="S128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T128" s="10" t="n">
-        <v>1</v>
+      <c r="T128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>9049</v>
+        <v>6893</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Leadership Outreach Toastmasters Club</t>
+          <t>Indy Free Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13195,8 +13195,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P129" s="9" t="n">
-        <v>0</v>
+      <c r="P129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -13207,26 +13207,26 @@
       <c r="S129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>7825542</v>
+        <v>9049</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Virtual Voices Aspiring Toastmasters Club</t>
+          <t>Leadership Outreach Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q130" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -13304,26 +13304,26 @@
       <c r="S130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="10" t="n">
-        <v>1</v>
+      <c r="T130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="10" t="n">
-        <v>1</v>
+      <c r="Z130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13337,19 +13337,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>3996334</v>
+        <v>7825542</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Indy Collegiate Communicators</t>
+          <t>Virtual Voices Aspiring Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -13392,8 +13392,8 @@
       <c r="P131" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" s="9" t="n">
-        <v>0</v>
+      <c r="Q131" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -13401,20 +13401,20 @@
       <c r="S131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T131" s="9" t="n">
-        <v>0</v>
+      <c r="T131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13438,15 +13438,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>6886302</v>
+        <v>3996334</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Indy Inspirations</t>
+          <t>Indy Collegiate Communicators</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13474,11 +13474,11 @@
         </is>
       </c>
       <c r="M132" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O132" s="7" t="inlineStr">
@@ -13487,10 +13487,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -13505,13 +13505,13 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -13519,8 +13519,8 @@
       <c r="Z132" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA132" s="9" t="n">
-        <v>0</v>
+      <c r="AA132" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>2156369</v>
+        <v>6886302</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Roadmasters</t>
+          <t>Indy Inspirations</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -13571,11 +13571,11 @@
         </is>
       </c>
       <c r="M133" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O133" s="7" t="inlineStr">
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13602,13 +13602,13 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -13616,8 +13616,8 @@
       <c r="Z133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA133" s="10" t="n">
-        <v>1</v>
+      <c r="AA133" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -13632,11 +13632,11 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>7966865</v>
+        <v>2156369</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Talk of the Trust</t>
+          <t>Roadmasters</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -13654,17 +13654,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
@@ -13699,13 +13699,13 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -13725,19 +13725,19 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>6602834</v>
+        <v>7966865</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Talk of the Trust</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -13796,19 +13796,19 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>1268920</v>
+        <v>6602834</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Got Toast?</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13851,10 +13851,10 @@
         <v>26</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13862,11 +13862,11 @@
         </is>
       </c>
       <c r="M136" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O136" s="7" t="inlineStr">
@@ -13892,23 +13892,23 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="10" t="n">
-        <v>4</v>
+      <c r="V136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="9" t="n">
-        <v>0</v>
+      <c r="X136" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -13923,11 +13923,11 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>7594</v>
+        <v>1268920</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Lilly Corp. Center Club</t>
+          <t>Got Toast?</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -13959,11 +13959,11 @@
         </is>
       </c>
       <c r="M137" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O137" s="7" t="inlineStr">
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -13989,14 +13989,14 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="9" t="n">
-        <v>1</v>
+      <c r="V137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X137" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14004,8 +14004,8 @@
       <c r="Z137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA137" s="10" t="n">
-        <v>1</v>
+      <c r="AA137" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -14020,11 +14020,11 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>583391</v>
+        <v>7594</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>LTC Toastmasters Club</t>
+          <t>Lilly Corp. Center Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L138" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
@@ -14087,13 +14087,13 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="9" t="n">
-        <v>3</v>
+      <c r="X138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
@@ -14117,39 +14117,39 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>6023</v>
+        <v>583391</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Twin Bridges Club</t>
+          <t>LTC Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J139" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K139" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F139" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G139" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="J139" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K139" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14166,10 +14166,10 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
@@ -14177,20 +14177,20 @@
       <c r="S139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T139" s="10" t="n">
-        <v>1</v>
+      <c r="T139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="10" t="n">
-        <v>7</v>
+      <c r="X139" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
@@ -14210,19 +14210,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>4081</v>
+        <v>6023</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Greater Greenwood Club 4081</t>
+          <t>Twin Bridges Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14262,11 +14262,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P140" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q140" s="10" t="n">
-        <v>2</v>
+      <c r="P140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q140" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -14281,13 +14281,13 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X140" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
@@ -14311,35 +14311,35 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>681</v>
+        <v>4081</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Greenwood Woodman Toastmasters Club</t>
+          <t>Greater Greenwood Club 4081</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J141" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K141" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="F141" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G141" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J141" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K141" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14359,32 +14359,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q141" s="9" t="n">
-        <v>1</v>
+      <c r="P141" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q141" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T141" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U141" s="10" t="n">
+      <c r="U141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="V141" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -14408,15 +14408,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>17</v>
+        <v>681</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Pioneer Club #17</t>
+          <t>Greenwood Woodman Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L142" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -14457,25 +14457,25 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U142" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -14505,15 +14505,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>1109991</v>
+        <v>17</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Vineyard Toastmasters</t>
+          <t>Pioneer Club #17</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K143" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -14557,7 +14557,7 @@
         <v>0</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -14565,11 +14565,11 @@
       <c r="S143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U143" s="10" t="n">
-        <v>1</v>
+      <c r="T143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
         <v>2</v>
@@ -14598,19 +14598,19 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>2481</v>
+        <v>1109991</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Columbus Club</t>
+          <t>Vineyard Toastmasters</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>1</v>
@@ -14660,16 +14660,16 @@
         <v>0</v>
       </c>
       <c r="S144" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
+      <c r="U144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -14680,8 +14680,8 @@
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>5904247</v>
+        <v>2481</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Cummins Toastmasters Club</t>
+          <t>Columbus Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,25 +14721,25 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L145" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O145" s="7" t="inlineStr">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>1</v>
@@ -14757,31 +14757,31 @@
         <v>0</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>1</v>
+      <c r="X145" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA145" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -14796,11 +14796,11 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>28679035</v>
+        <v>5904247</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Good to Great Toastmasters</t>
+          <t>Cummins Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -14832,11 +14832,11 @@
         </is>
       </c>
       <c r="M146" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O146" s="7" t="inlineStr">
@@ -14863,13 +14863,13 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X146" s="10" t="n">
-        <v>4</v>
+      <c r="X146" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
@@ -14877,8 +14877,8 @@
       <c r="Z146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA146" s="10" t="n">
-        <v>1</v>
+      <c r="AA146" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>28675676</v>
+        <v>28679035</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>NPG Toastmasters</t>
+          <t>Good to Great Toastmasters</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -14944,8 +14944,8 @@
       <c r="P147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" s="10" t="n">
-        <v>2</v>
+      <c r="Q147" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -14960,13 +14960,13 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="9" t="n">
-        <v>3</v>
+      <c r="X147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -14990,15 +14990,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1588093</v>
+        <v>28675676</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Power Speakers</t>
+          <t>NPG Toastmasters</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,25 +15012,25 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O148" s="7" t="inlineStr">
@@ -15039,10 +15039,10 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q148" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q148" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -15050,20 +15050,20 @@
       <c r="S148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T148" s="10" t="n">
-        <v>1</v>
+      <c r="T148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="9" t="n">
-        <v>3</v>
+      <c r="X148" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15071,8 +15071,8 @@
       <c r="Z148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA148" s="9" t="n">
-        <v>0</v>
+      <c r="AA148" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -15083,93 +15083,93 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>482</v>
+        <v>1588093</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Bloomington Good Morning Club</t>
+          <t>Power Speakers</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J149" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K149" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M149" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O149" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F149" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G149" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J149" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M149" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N149" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O149" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U149" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X149" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z149" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA149" s="10" t="n">
-        <v>1</v>
+      <c r="AA149" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>6724498</v>
+        <v>482</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Clay On Words Toastmasters</t>
+          <t>Bloomington Good Morning Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K150" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L150" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>1</v>
@@ -15244,11 +15244,11 @@
       <c r="S150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
+      <c r="T150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V150" s="9" t="n">
         <v>0</v>
@@ -15256,8 +15256,8 @@
       <c r="W150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X150" s="9" t="n">
-        <v>3</v>
+      <c r="X150" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
@@ -15281,15 +15281,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>28678220</v>
+        <v>6724498</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Cookmasters</t>
+          <t>Clay On Words Toastmasters</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,10 +15303,10 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K151" s="4" t="n">
         <v>0</v>
@@ -15317,11 +15317,11 @@
         </is>
       </c>
       <c r="M151" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O151" s="7" t="inlineStr">
@@ -15330,10 +15330,10 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -15354,7 +15354,7 @@
         <v>0</v>
       </c>
       <c r="X151" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -15362,8 +15362,8 @@
       <c r="Z151" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA151" s="9" t="n">
-        <v>0</v>
+      <c r="AA151" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -15378,11 +15378,11 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>2471</v>
+        <v>28678220</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Good Evening Toastmasters Club</t>
+          <t>Cookmasters</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15414,11 +15414,11 @@
         </is>
       </c>
       <c r="M152" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O152" s="7" t="inlineStr">
@@ -15445,22 +15445,22 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA152" s="10" t="n">
-        <v>1</v>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA152" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -15475,11 +15475,11 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>6754</v>
+        <v>2471</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>High Noon Toastmasters Club #6754</t>
+          <t>Good Evening Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>0</v>
       </c>
       <c r="S153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T153" s="9" t="n">
         <v>0</v>
@@ -15542,13 +15542,13 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X153" s="10" t="n">
-        <v>6</v>
+      <c r="X153" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
@@ -15563,24 +15563,24 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>5212</v>
+        <v>6754</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>5212 Toastmasters</t>
+          <t>High Noon Toastmasters Club #6754</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,10 +15594,10 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K154" s="4" t="n">
         <v>0</v>
@@ -15608,11 +15608,11 @@
         </is>
       </c>
       <c r="M154" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O154" s="7" t="inlineStr">
@@ -15630,7 +15630,7 @@
         <v>0</v>
       </c>
       <c r="S154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T154" s="9" t="n">
         <v>0</v>
@@ -15644,17 +15644,17 @@
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X154" s="9" t="n">
-        <v>0</v>
+      <c r="X154" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA154" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -15669,11 +15669,11 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>1127</v>
+        <v>5212</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Donald A. Campbell Lafayette Toastmasters Club</t>
+          <t>5212 Toastmasters</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K155" s="4" t="n">
         <v>0</v>
@@ -15705,11 +15705,11 @@
         </is>
       </c>
       <c r="M155" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O155" s="7" t="inlineStr">
@@ -15742,7 +15742,7 @@
         <v>0</v>
       </c>
       <c r="X155" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
@@ -15750,8 +15750,8 @@
       <c r="Z155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA155" s="10" t="n">
-        <v>1</v>
+      <c r="AA155" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -15766,15 +15766,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>5882</v>
+        <v>1127</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Tippecanoe Talkers Club</t>
+          <t>Donald A. Campbell Lafayette Toastmasters Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,10 +15788,10 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K156" s="4" t="n">
         <v>0</v>
@@ -15815,19 +15815,19 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q156" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T156" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U156" s="9" t="n">
         <v>0</v>
@@ -15838,8 +15838,8 @@
       <c r="W156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X156" s="10" t="n">
-        <v>5</v>
+      <c r="X156" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
@@ -15863,15 +15863,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>6098430</v>
+        <v>5882</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>ToastCATsters</t>
+          <t>Tippecanoe Talkers Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -15912,31 +15912,31 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X157" s="9" t="n">
-        <v>1</v>
+      <c r="X157" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>4685166</v>
+        <v>6098430</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters at Purdue</t>
+          <t>ToastCATsters</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K158" s="4" t="n">
         <v>1</v>
@@ -15996,11 +15996,11 @@
         </is>
       </c>
       <c r="M158" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O158" s="7" t="inlineStr">
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q158" s="9" t="n">
         <v>0</v>
@@ -16020,8 +16020,8 @@
       <c r="S158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T158" s="10" t="n">
-        <v>1</v>
+      <c r="T158" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U158" s="9" t="n">
         <v>0</v>
@@ -16032,17 +16032,17 @@
       <c r="W158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X158" s="10" t="n">
-        <v>5</v>
+      <c r="X158" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA158" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -16057,11 +16057,11 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>4564</v>
+        <v>4685166</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Top of the Morning Club</t>
+          <t>Toastmasters at Purdue</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
@@ -16079,35 +16079,35 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K159" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M159" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O159" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P159" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L159" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M159" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N159" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O159" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P159" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
       </c>
@@ -16115,16 +16115,16 @@
         <v>0</v>
       </c>
       <c r="S159" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T159" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U159" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -16138,8 +16138,8 @@
       <c r="Z159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA159" s="10" t="n">
-        <v>1</v>
+      <c r="AA159" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -16150,19 +16150,19 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>7080054</v>
+        <v>4564</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Brick Street Toastmasters</t>
+          <t>Top of the Morning Club</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,17 +16176,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K160" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L160" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q160" s="9" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="S160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U160" s="9" t="n">
         <v>0</v>
@@ -16227,7 +16227,7 @@
         <v>0</v>
       </c>
       <c r="X160" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
@@ -16251,15 +16251,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>5680</v>
+        <v>7080054</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Corteva Indy Club</t>
+          <t>Brick Street Toastmasters</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q161" s="9" t="n">
         <v>0</v>
@@ -16311,20 +16311,20 @@
       <c r="S161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U161" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X161" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
@@ -16348,11 +16348,11 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>1183</v>
+        <v>5680</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Nora Toastmasters By the Pyramids</t>
+          <t>Corteva Indy Club</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
@@ -16370,17 +16370,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L162" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -16421,7 +16421,7 @@
         <v>0</v>
       </c>
       <c r="X162" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
@@ -16445,15 +16445,15 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>28675702</v>
+        <v>1183</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Presenters @ Polaris</t>
+          <t>Nora Toastmasters By the Pyramids</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -16517,14 +16517,14 @@
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X163" s="9" t="n">
-        <v>1</v>
+      <c r="X163" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -16542,15 +16542,15 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>28677632</v>
+        <v>28675702</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Transformers</t>
+          <t>Presenters @ Polaris</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16564,17 +16564,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K164" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="8" t="n">
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q164" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R164" s="9" t="n">
         <v>0</v>
@@ -16615,13 +16615,13 @@
         <v>0</v>
       </c>
       <c r="X164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -16635,19 +16635,19 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>621</v>
+        <v>28677632</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Logansport Toastmasters Club</t>
+          <t>Transformers</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -16661,17 +16661,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K165" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L165" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M165" s="8" t="n">
@@ -16688,10 +16688,10 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>0</v>
@@ -16711,14 +16711,14 @@
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X165" s="10" t="n">
-        <v>4</v>
+      <c r="X165" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -16736,15 +16736,15 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>9666</v>
+        <v>621</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Polished Brash Club</t>
+          <t>Logansport Toastmasters Club</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -16758,17 +16758,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
@@ -16785,25 +16785,25 @@
         </is>
       </c>
       <c r="P166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q166" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S166" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T166" s="10" t="n">
-        <v>1</v>
+      <c r="S166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V166" s="10" t="n">
-        <v>4</v>
+      <c r="V166" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -16833,15 +16833,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>7520148</v>
+        <v>9666</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Power Talkers</t>
+          <t>Polished Brash Club</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -16858,10 +16858,10 @@
         <v>22</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -16885,28 +16885,28 @@
         <v>0</v>
       </c>
       <c r="Q167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" s="9" t="n">
-        <v>0</v>
+      <c r="S167" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>1</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X167" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
@@ -16930,15 +16930,15 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>28679550</v>
+        <v>7520148</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>The Smooth Talkers</t>
+          <t>Power Talkers</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -16966,11 +16966,11 @@
         </is>
       </c>
       <c r="M168" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N168" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O168" s="7" t="inlineStr">
@@ -16997,22 +16997,22 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X168" s="9" t="n">
-        <v>0</v>
+      <c r="X168" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA168" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -17027,15 +17027,15 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>1845527</v>
+        <v>28679550</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Westfield Toastmasters Club</t>
+          <t>The Smooth Talkers</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17063,11 +17063,11 @@
         </is>
       </c>
       <c r="M169" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O169" s="7" t="inlineStr">
@@ -17094,22 +17094,22 @@
         <v>0</v>
       </c>
       <c r="V169" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="10" t="n">
-        <v>6</v>
+      <c r="X169" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z169" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA169" s="10" t="n">
-        <v>1</v>
+      <c r="Z169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA169" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -17120,15 +17120,15 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>3347</v>
+        <v>1845527</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Classic Communicators Club #3347</t>
+          <t>Westfield Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -17146,17 +17146,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M170" s="8" t="n">
@@ -17191,13 +17191,13 @@
         <v>0</v>
       </c>
       <c r="V170" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X170" s="9" t="n">
-        <v>3</v>
+      <c r="X170" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -17221,15 +17221,15 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>1820966</v>
+        <v>3347</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Key Master Communicators</t>
+          <t>Classic Communicators Club #3347</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -17243,10 +17243,10 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K171" s="4" t="n">
         <v>1</v>
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q171" s="9" t="n">
         <v>0</v>
@@ -17293,14 +17293,14 @@
       <c r="W171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X171" s="10" t="n">
-        <v>5</v>
+      <c r="X171" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z171" s="9" t="n">
-        <v>0</v>
+      <c r="Z171" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA171" s="10" t="n">
         <v>1</v>
@@ -17318,11 +17318,11 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>2000</v>
+        <v>1820966</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Northeast 2000 Club</t>
+          <t>Key Master Communicators</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>0</v>
@@ -17385,13 +17385,13 @@
         <v>0</v>
       </c>
       <c r="V172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X172" s="9" t="n">
-        <v>2</v>
+      <c r="X172" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y172" s="9" t="n">
         <v>0</v>
@@ -17415,11 +17415,11 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>6515</v>
+        <v>2000</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Roche Indianapolis Toastmasters</t>
+          <t>Northeast 2000 Club</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
@@ -17437,17 +17437,17 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L173" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M173" s="8" t="n">
@@ -17464,7 +17464,7 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q173" s="9" t="n">
         <v>0</v>
@@ -17482,13 +17482,13 @@
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X173" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W173" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X173" s="10" t="n">
-        <v>4</v>
       </c>
       <c r="Y173" s="9" t="n">
         <v>0</v>
@@ -17512,39 +17512,39 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>5187</v>
+        <v>6515</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>St. Luke's Toastmasters Club</t>
+          <t>Roche Indianapolis Toastmasters</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G174" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J174" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K174" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F174" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G174" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J174" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -17561,31 +17561,31 @@
         </is>
       </c>
       <c r="P174" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T174" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V174" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X174" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y174" s="9" t="n">
         <v>0</v>
@@ -17609,11 +17609,11 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>5763</v>
+        <v>5187</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Fishers</t>
+          <t>St. Luke's Toastmasters Club</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
@@ -17631,17 +17631,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q175" s="9" t="n">
         <v>0</v>
@@ -17669,20 +17669,20 @@
       <c r="S175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T175" s="9" t="n">
-        <v>0</v>
+      <c r="T175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="10" t="n">
-        <v>4</v>
+      <c r="V175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W175" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X175" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y175" s="9" t="n">
         <v>0</v>
@@ -17702,19 +17702,19 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>1155</v>
+        <v>5763</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Daybreakers Club</t>
+          <t>Toastmasters Club of Fishers</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -17728,13 +17728,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -17758,13 +17758,13 @@
         <v>1</v>
       </c>
       <c r="Q176" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S176" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T176" s="9" t="n">
         <v>0</v>
@@ -17772,11 +17772,11 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="9" t="n">
-        <v>0</v>
+      <c r="V176" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W176" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X176" s="10" t="n">
         <v>5</v>
@@ -17803,15 +17803,15 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>4083</v>
+        <v>1155</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Fort Harrison Toastmasters Club</t>
+          <t>Daybreakers Club</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17825,17 +17825,17 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L177" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M177" s="8" t="n">
@@ -17852,31 +17852,31 @@
         </is>
       </c>
       <c r="P177" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T177" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X177" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -17900,15 +17900,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>3326</v>
+        <v>4083</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Greenfield Toastmaster Club</t>
+          <t>Fort Harrison Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -17922,13 +17922,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q178" s="9" t="n">
         <v>0</v>
@@ -17960,20 +17960,20 @@
       <c r="S178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T178" s="9" t="n">
-        <v>0</v>
+      <c r="T178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X178" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
@@ -17997,15 +17997,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>725166</v>
+        <v>3326</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>T.A.L.K.S. Club</t>
+          <t>Greenfield Toastmaster Club</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18019,10 +18019,10 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K179" s="4" t="n">
         <v>0</v>
@@ -18057,11 +18057,11 @@
       <c r="S179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T179" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U179" s="10" t="n">
-        <v>1</v>
+      <c r="T179" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
         <v>0</v>
@@ -18070,7 +18070,7 @@
         <v>0</v>
       </c>
       <c r="X179" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
@@ -18094,15 +18094,15 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>3920</v>
+        <v>725166</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Turning Point Toastmasters Club</t>
+          <t>T.A.L.K.S. Club</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -18116,17 +18116,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
@@ -18152,35 +18152,132 @@
         <v>0</v>
       </c>
       <c r="S180" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T180" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U180" s="9" t="n">
-        <v>0</v>
+      <c r="U180" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X180" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA180" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="n">
+        <v>3920</v>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>Turning Point Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G181" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J181" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K181" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X180" s="10" t="n">
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M181" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O181" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T181" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z180" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA180" s="10" t="n">
+      <c r="Y181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA181" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA180"/>
+  <autoFilter ref="A1:AA181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18267,7 +18364,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18366,7 +18463,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18399,7 +18496,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18432,7 +18529,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -18465,7 +18562,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18498,7 +18595,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18531,7 +18628,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18564,7 +18661,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18597,7 +18694,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18630,7 +18727,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -18663,7 +18760,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18693,16 +18790,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -18762,7 +18859,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18795,7 +18892,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -18828,13 +18925,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -18894,7 +18991,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19026,7 +19123,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -19191,7 +19288,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19224,7 +19321,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19257,7 +19354,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19290,7 +19387,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -19323,7 +19420,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -19356,7 +19453,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 31 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 31 clubs short</t>
         </is>
       </c>
     </row>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1238,17 +1238,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1432,17 +1432,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1558,11 +1558,11 @@
       <c r="P9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="9" t="n">
-        <v>1</v>
+      <c r="Q9" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="10" t="n">
         <v>2</v>
@@ -1820,17 +1820,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2543,11 +2543,11 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>3</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>4</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="10" t="n">
         <v>2</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4095,8 +4095,8 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>3</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4477,8 +4477,8 @@
       <c r="S39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="9" t="n">
-        <v>0</v>
+      <c r="T39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4730,17 +4730,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4777,8 +4777,8 @@
       <c r="V42" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W42" s="9" t="n">
-        <v>3</v>
+      <c r="W42" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>6</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>1</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7199,11 +7199,11 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>2</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>5</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>4</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>1</v>
@@ -8842,11 +8842,11 @@
       <c r="S84" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
+      <c r="T84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
         <v>3</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9330,8 +9330,8 @@
       <c r="T89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
+      <c r="U89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V89" s="9" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="U91" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V91" s="9" t="n">
         <v>3</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9624,8 +9624,8 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>3</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10600,8 +10600,8 @@
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>3</v>
+      <c r="X102" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10979,8 +10979,8 @@
       <c r="T106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
+      <c r="U106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V106" s="9" t="n">
         <v>1</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>2</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="10" t="n">
         <v>2</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>4</v>
       </c>
       <c r="W117" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>4</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13110,8 +13110,8 @@
       <c r="S128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
@@ -13496,7 +13496,7 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T132" s="10" t="n">
         <v>1</v>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13683,8 +13683,8 @@
       <c r="P134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" s="9" t="n">
-        <v>1</v>
+      <c r="Q134" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="9" t="n">
         <v>0</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -17872,8 +17872,8 @@
       <c r="V177" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W177" s="9" t="n">
-        <v>3</v>
+      <c r="W177" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X177" s="10" t="n">
         <v>5</v>
@@ -18310,13 +18310,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>4</v>
       </c>
       <c r="W182" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X182" s="10" t="n">
         <v>5</v>
@@ -18476,7 +18476,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -18494,13 +18494,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -18560,7 +18560,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -18659,7 +18659,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18692,7 +18692,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18707,7 +18707,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -18857,7 +18857,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18956,7 +18956,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18989,7 +18989,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19022,7 +19022,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -19088,7 +19088,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19253,7 +19253,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19286,7 +19286,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19550,7 +19550,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/215/inyear.xlsx
+++ b/docs/d/215/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 31 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 31 clubs short</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1282,8 +1282,8 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>1</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>1</v>
@@ -2437,8 +2437,8 @@
       <c r="R18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="9" t="n">
-        <v>1</v>
+      <c r="S18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T18" s="10" t="n">
         <v>1</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2725,8 +2725,8 @@
       <c r="Q21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R21" s="9" t="n">
-        <v>1</v>
+      <c r="R21" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>0</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>4</v>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6035,8 +6035,8 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>3</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7834,17 +7834,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>11</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -7878,11 +7878,11 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W74" s="9" t="n">
-        <v>0</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W74" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>5</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10588,8 +10588,8 @@
       <c r="S102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10876,8 +10876,8 @@
       <c r="R105" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S105" s="9" t="n">
-        <v>1</v>
+      <c r="S105" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T105" s="10" t="n">
         <v>1</v>
@@ -11071,7 +11071,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" s="10" t="n">
         <v>1</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11361,8 +11361,8 @@
       <c r="R110" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S110" s="9" t="n">
-        <v>1</v>
+      <c r="S110" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T110" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11564,11 +11564,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X112" s="9" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>4</v>
       </c>
       <c r="W117" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>4</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" s="9" t="n">
         <v>0</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>7</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>1</v>
@@ -14378,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
         <v>1</v>
       </c>
       <c r="U143" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V143" s="9" t="n">
         <v>1</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16567,10 +16567,10 @@
         <v>8</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
@@ -17825,10 +17825,10 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K177" s="4" t="n">
         <v>-2</v>
@@ -18461,7 +18461,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18560,7 +18560,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -18791,7 +18791,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18890,7 +18890,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18905,7 +18905,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -19055,7 +19055,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19088,13 +19088,13 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -19121,13 +19121,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
